--- a/Retrieval_A.xlsx
+++ b/Retrieval_A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Fernanda/Library/CloudStorage/Box-Box/Leal Lab/Shared Resources/New Emotional Image Sets/A+B NEW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc151/Library/CloudStorage/Box-Box/Leal Lab/Shared Resources/New Emotional Image Sets/Emotional MDT_A+B Sets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A022FA2-1C2C-7249-BF99-9B62FDD3171D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4FD035-1E0B-1743-B833-0D0496A7F808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="3940" windowWidth="28800" windowHeight="16520" xr2:uid="{EAA8ADB9-3654-A645-A44E-1FF4666E82B0}"/>
+    <workbookView xWindow="9000" yWindow="3940" windowWidth="13100" windowHeight="16520" xr2:uid="{EAA8ADB9-3654-A645-A44E-1FF4666E82B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>3114_D_X.jpg</t>
   </si>
   <si>
-    <t>351B.jpg</t>
-  </si>
-  <si>
     <t>1116_D_X.jpg</t>
   </si>
   <si>
@@ -130,9 +127,6 @@
     <t>2099_D_X.jpg</t>
   </si>
   <si>
-    <t>30003a.jpg</t>
-  </si>
-  <si>
     <t>3112_D_X.jpg</t>
   </si>
   <si>
@@ -208,9 +202,6 @@
     <t>2085_C_X.jpg</t>
   </si>
   <si>
-    <t>354a.jpg</t>
-  </si>
-  <si>
     <t>2092_D_X.jpg</t>
   </si>
   <si>
@@ -319,9 +310,6 @@
     <t>2045_B_L.jpg</t>
   </si>
   <si>
-    <t>1054_B_L.jpg</t>
-  </si>
-  <si>
     <t>2003_B_H.jpg</t>
   </si>
   <si>
@@ -331,9 +319,6 @@
     <t>2100_D_X.jpg</t>
   </si>
   <si>
-    <t>366B.jpg</t>
-  </si>
-  <si>
     <t>3055_B_L.jpg</t>
   </si>
   <si>
@@ -343,9 +328,6 @@
     <t>3079_C_X.jpg</t>
   </si>
   <si>
-    <t>306D.jpg</t>
-  </si>
-  <si>
     <t>2041_B_L.jpg</t>
   </si>
   <si>
@@ -379,9 +361,6 @@
     <t>2113_D_X.jpg</t>
   </si>
   <si>
-    <t>1055_B_L.jpg</t>
-  </si>
-  <si>
     <t>2032_B_H.jpg</t>
   </si>
   <si>
@@ -430,9 +409,6 @@
     <t>3046_B_H.jpg</t>
   </si>
   <si>
-    <t>601X.jpg</t>
-  </si>
-  <si>
     <t>2105_D_X.jpg</t>
   </si>
   <si>
@@ -538,10 +514,34 @@
     <t>2024_B_L.jpg</t>
   </si>
   <si>
-    <t>320F.jpg</t>
-  </si>
-  <si>
-    <t>359B.jpg</t>
+    <t>1054_B_H.jpg</t>
+  </si>
+  <si>
+    <t>1055_B_H.jpg</t>
+  </si>
+  <si>
+    <t>3107_D_X.jpg</t>
+  </si>
+  <si>
+    <t>1015_B_H.jpg</t>
+  </si>
+  <si>
+    <t>1047_B_L.jpg</t>
+  </si>
+  <si>
+    <t>1039_A_L.jpg</t>
+  </si>
+  <si>
+    <t>1067_C_X.jpg</t>
+  </si>
+  <si>
+    <t>1044_B_H.jpg</t>
+  </si>
+  <si>
+    <t>1001_B_L.jpg</t>
+  </si>
+  <si>
+    <t>1073_C_X.jpg</t>
   </si>
 </sst>
 </file>
@@ -557,10 +557,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="13"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -571,20 +572,11 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="7"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -606,15 +598,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -965,10 +959,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -978,53 +972,53 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
+      <c r="A3" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -1035,7 +1029,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
@@ -1049,24 +1043,24 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
@@ -1077,21 +1071,21 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -1105,10 +1099,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1119,21 +1113,21 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
@@ -1146,67 +1140,67 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>29</v>
+      <c r="A15" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>129</v>
+      <c r="A18" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>72</v>
+      <c r="A19" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>1</v>
@@ -1216,67 +1210,67 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>122</v>
+      <c r="A20" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>164</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>14</v>
+      <c r="A23" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>1</v>
@@ -1287,10 +1281,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1300,67 +1294,67 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>105</v>
+      <c r="A26" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>123</v>
+      <c r="A29" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>1</v>
@@ -1371,21 +1365,21 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
@@ -1394,15 +1388,15 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
@@ -1413,203 +1407,203 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>31</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
@@ -1623,24 +1617,24 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>2</v>
@@ -1651,105 +1645,105 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>75</v>
+      <c r="A55" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>6</v>
@@ -1763,38 +1757,38 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -1805,52 +1799,52 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
-        <v>21</v>
+      <c r="A63" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>50</v>
+        <v>162</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -1860,134 +1854,134 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>58</v>
+      <c r="A66" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>6</v>
@@ -2001,24 +1995,24 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>1</v>
@@ -2029,21 +2023,21 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>6</v>
@@ -2057,35 +2051,35 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>142</v>
+      <c r="A81" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>5</v>
@@ -2098,53 +2092,53 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
-        <v>124</v>
+      <c r="A83" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>2</v>
@@ -2155,66 +2149,66 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>25</v>
+      <c r="A88" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>16</v>
+      <c r="A90" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>140</v>
+      <c r="A91" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>1</v>
@@ -2224,11 +2218,11 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>131</v>
+      <c r="A92" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -2239,7 +2233,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>6</v>
@@ -2248,141 +2242,141 @@
         <v>1</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>2</v>
@@ -2392,11 +2386,11 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
-        <v>91</v>
+      <c r="A104" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>2</v>
@@ -2407,52 +2401,52 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
@@ -2463,52 +2457,52 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>1</v>
@@ -2519,21 +2513,21 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>7</v>
@@ -2542,57 +2536,57 @@
         <v>1</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -2603,7 +2597,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>5</v>
@@ -2612,43 +2606,43 @@
         <v>1</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
@@ -2659,10 +2653,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>1</v>
@@ -2673,24 +2667,24 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
@@ -2701,122 +2695,122 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>1</v>
@@ -2826,36 +2820,36 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" s="3" t="s">
-        <v>97</v>
+      <c r="A135" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>7</v>
@@ -2869,24 +2863,24 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -2897,49 +2891,49 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>7</v>
@@ -2953,91 +2947,91 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>6</v>
@@ -3051,77 +3045,77 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
-        <v>98</v>
+      <c r="A153" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A156" s="5" t="s">
-        <v>13</v>
+      <c r="A156" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>7</v>
@@ -3135,30 +3129,30 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
